--- a/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260918.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/00878/ETF_Investment_Portfolio_20260918.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>10.05%</t>
+          <t>9.76%</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>9.44%</t>
+          <t>9.37%</t>
         </is>
       </c>
     </row>
@@ -660,7 +660,7 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>6.49%</t>
+          <t>6.38%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>5.72%</t>
+          <t>5.77%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>4.30%</t>
+          <t>4.52%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.07%</t>
+          <t>4.08%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>4.05%</t>
+          <t>4.00%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.54%</t>
+          <t>3.69%</t>
         </is>
       </c>
     </row>
@@ -792,24 +792,24 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>3.29%</t>
+          <t>3.26%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>2379</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>富邦金</t>
+          <t>瑞昱</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>132,826,945</t>
+          <t>27,829,000</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
@@ -821,17 +821,17 @@
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>2379</t>
+          <t>2881</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>瑞昱</t>
+          <t>富邦金</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>27,829,000</t>
+          <t>132,826,945</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
@@ -843,44 +843,44 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2301</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>光寶科</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>354,020,964</t>
+          <t>64,742,000</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.81%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>2301</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>光寶科</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>64,742,000</t>
+          <t>354,020,964</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>2.75%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.71%</t>
+          <t>2.76%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>2.52%</t>
+          <t>2.61%</t>
         </is>
       </c>
     </row>
@@ -946,7 +946,7 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.60%</t>
         </is>
       </c>
     </row>
@@ -968,24 +968,24 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>2.51%</t>
+          <t>2.55%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>3045</t>
+          <t>2885</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>台灣大</t>
+          <t>元大金</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>131,081,000</t>
+          <t>233,108,056</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
@@ -997,22 +997,22 @@
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>2885</t>
+          <t>3045</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>元大金</t>
+          <t>台灣大</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>233,108,056</t>
+          <t>131,081,000</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>2.46%</t>
+          <t>2.48%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>2.41%</t>
+          <t>2.40%</t>
         </is>
       </c>
     </row>
@@ -1078,7 +1078,7 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>2.27%</t>
+          <t>2.24%</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1100,7 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>2.20%</t>
+          <t>2.19%</t>
         </is>
       </c>
     </row>
@@ -1122,24 +1122,24 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.12%</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>5876</t>
+          <t>2376</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>上海商銀</t>
+          <t>技嘉</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>254,199,845</t>
+          <t>35,705,000</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
@@ -1151,22 +1151,22 @@
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>2376</t>
+          <t>5876</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>技嘉</t>
+          <t>上海商銀</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>35,705,000</t>
+          <t>254,199,845</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>1.94%</t>
+          <t>1.91%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>1.78%</t>
+          <t>1.76%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>1.75%</t>
+          <t>1.73%</t>
         </is>
       </c>
     </row>
@@ -1254,7 +1254,7 @@
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.53%</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>10,132,136,383</t>
+          <t>10,126,443,012</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr"/>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>6,489,596,429</t>
+          <t>6,832,041,029</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr"/>
